--- a/project/excel/nist_sp_800_53.xlsx
+++ b/project/excel/nist_sp_800_53.xlsx
@@ -496,14 +496,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>baseline_level</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>baseline_level</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
           <t>baseline_controls</t>
@@ -512,7 +512,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"LOW,MODERATE,HIGH,PRIVACY"</formula1>
     </dataValidation>
   </dataValidations>
@@ -532,115 +532,115 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>family_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>family_controls</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>control_identifier</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>family_id</t>
+          <t>control_statement</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>family_controls</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>control_statement</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
           <t>control_discussion</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>control_parameters</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>related_control_ids</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>control_references</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>assessment_objective</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>assessment_methods</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>control_status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>incorporated_into</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>moved_to</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>withdrawal_reason</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>implementation_level</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>contributes_to_assurance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>control_identifier</t>
-        </is>
-      </c>
       <c r="P1" t="inlineStr">
         <is>
           <t>control_enhancements</t>
@@ -649,10 +649,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"WITHDRAWN"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ORGANIZATION,SYSTEM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -672,79 +672,79 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>enhancement_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>control_statement</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>control_discussion</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>control_parameters</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>related_control_ids</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>control_references</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>assessment_objective</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>assessment_methods</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>control_status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>incorporated_into</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>moved_to</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>withdrawal_reason</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>implementation_level</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>contributes_to_assurance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>enhancement_id</t>
-        </is>
-      </c>
       <c r="P1" t="inlineStr">
         <is>
           <t>required_controls</t>
@@ -753,10 +753,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"WITHDRAWN"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ORGANIZATION,SYSTEM"</formula1>
     </dataValidation>
   </dataValidations>
